--- a/docs/engineer_books/Юго-восток Инженеры.xlsx
+++ b/docs/engineer_books/Юго-восток Инженеры.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Московская область, г. Кашира, ул. Ленина, д. 10</t>
+          <t>Московская область, г. Кашира, ул. Ленина, д. 13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Московская область, г. Кашира, ул. Ленина, д. 12</t>
+          <t>Московская область, г. Кашира, ул. Ленина, д. 15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Московская область, г. Домодедово, Каширское шоссе, д. 15</t>
+          <t>Московская область, г. Домодедово, Каширское шоссе, д. 17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
